--- a/ga4_bq_export.xlsx
+++ b/ga4_bq_export.xlsx
@@ -43,39 +43,39 @@
     <font>
       <name val="Arial"/>
       <color rgb="00374151"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="001155CC"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001A3A6B"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003D6BB5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F5FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -144,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -161,19 +156,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -605,12 +597,12 @@
           <t>event_params</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>event_params</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>イベントパラメータ（REPEATED RECORD）。UNNEST(event_params) で展開。</t>
         </is>
@@ -639,12 +631,12 @@
           <t>device</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>device</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>デバイス情報（RECORD）。</t>
         </is>
@@ -673,12 +665,12 @@
           <t>traffic_source</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>traffic_source / collected_traffic_source</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>トラフィックソース情報。</t>
         </is>
@@ -707,12 +699,12 @@
           <t>items</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>商品リスト（REPEATED RECORD）。UNNEST(items) で展開。</t>
         </is>
@@ -772,34 +764,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>stream / platform / app_info</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -833,27 +825,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>プラットフォーム（Web / IOS / Android）</t>
         </is>
@@ -887,27 +879,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>app_info.firebase_app_id</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Firebase App ID</t>
         </is>
@@ -941,27 +933,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>app_info.version</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>アプリバージョン</t>
         </is>
@@ -992,34 +984,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1053,27 +1045,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>event_timestamp</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>イベント受信時刻（マイクロ秒、UTC）</t>
         </is>
@@ -1107,27 +1099,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>event_name</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>イベント名（page_view, purchase 等）</t>
         </is>
@@ -1161,27 +1153,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>event_bundle_sequence_id</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>バンドルのシーケンスID</t>
         </is>
@@ -1215,27 +1207,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>batch_event_index</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>バッチ内のイベント順序番号</t>
         </is>
@@ -1269,27 +1261,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>batch_page_id</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>ページごとのシーケンス番号</t>
         </is>
@@ -1320,34 +1312,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>event_params</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1381,27 +1373,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>event_params.value.string_value</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>文字列値（URL、キャンペーン名等）</t>
         </is>
@@ -1435,27 +1427,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>event_params.value.double_value</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>倍精度浮動小数点値</t>
         </is>
@@ -1513,34 +1505,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -1574,27 +1566,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>user_pseudo_id</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>擬似ID（アプリインスタンスID / ブラウザのclient_id相当）</t>
         </is>
@@ -1628,405 +1620,405 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>is_active_user</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>その日にアクティブだったか（日次テーブルのみ）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>privacy_info</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>同意モード情報</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>5-1</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ ads_storage</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>広告ターゲティング有効か（Yes / No / Unset）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>5-2</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ analytics_storage</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Analytics保存有効か</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>5-3</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ uses_transient_token</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>一時トークンを使用しているか</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>user_properties</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>REPEATED</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>REPEATED</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>ユーザープロパティ（REPEATED RECORD）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>6-1</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ key</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>プロパティ名</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>6-2</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ value.string_value</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>文字列値</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>6-3</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ value.int_value</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ INTEGER</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>整数値</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ value.double_value</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ FLOAT</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>倍精度値</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>6-5</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ value.float_value</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ FLOAT</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>浮動小数点値（現在未使用）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>6-6</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ value.set_timestamp_micros</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ INTEGER</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>最終設定時刻（マイクロ秒）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>user_ltv</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>RECORD</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>ユーザーLTV（日次テーブルのみ）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>7-1</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ revenue</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ FLOAT</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>LTV収益</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>7-2</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ currency</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  └ STRING</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>LTV通貨</t>
         </is>
@@ -2057,34 +2049,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>device</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -2118,27 +2110,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>device.mobile_brand_name</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>デバイスブランド名</t>
         </is>
@@ -2172,27 +2164,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>device.mobile_marketing_name</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>デバイスマーケティング名</t>
         </is>
@@ -2226,27 +2218,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>device.operating_system</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>OS名</t>
         </is>
@@ -2280,27 +2272,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>device.vendor_id</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>IDFV（IDFAが未収集の場合のみ）</t>
         </is>
@@ -2334,27 +2326,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>device.language</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>OS言語</t>
         </is>
@@ -2388,27 +2380,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>device.is_limited_ad_tracking</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>BOOLEAN</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>広告トラッキング制限設定</t>
         </is>
@@ -2442,27 +2434,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>device.web_info.browser_version</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>ブラウザバージョン</t>
         </is>
@@ -2520,34 +2512,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>geo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -2581,27 +2573,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>geo.sub_continent</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>亜大陸</t>
         </is>
@@ -2635,27 +2627,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>geo.region</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>地域</t>
         </is>
@@ -2689,27 +2681,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>geo.city</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>都市</t>
         </is>
@@ -2740,34 +2732,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>traffic_source / collected_traffic_source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -2781,27 +2773,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>traffic_source.name</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>初回獲得キャンペーン名</t>
         </is>
@@ -2835,27 +2827,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>traffic_source.source</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>初回獲得ソース</t>
         </is>
@@ -2869,27 +2861,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.manual_campaign_id</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>utm_id</t>
         </is>
@@ -2923,27 +2915,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.manual_source</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>utm_source</t>
         </is>
@@ -2977,27 +2969,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.manual_term</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>utm_term</t>
         </is>
@@ -3031,27 +3023,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.manual_creative_format</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>utm_creative_format</t>
         </is>
@@ -3085,27 +3077,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.manual_source_platform</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>utm_source_platform</t>
         </is>
@@ -3139,27 +3131,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>collected_traffic_source.dclid</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>DoubleClick Click Identifier</t>
         </is>
@@ -3217,34 +3209,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ecommerce</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -3278,27 +3270,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ecommerce.purchase_revenue_in_usd</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>購入収益（USD）※purchaseイベントのみ</t>
         </is>
@@ -3332,27 +3324,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>ecommerce.refund_value_in_usd</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>返金額（USD）※refundイベントのみ</t>
         </is>
@@ -3386,27 +3378,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>ecommerce.shipping_value_in_usd</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>送料（USD）</t>
         </is>
@@ -3440,27 +3432,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>ecommerce.tax_value_in_usd</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>税額（USD）</t>
         </is>
@@ -3494,27 +3486,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>ecommerce.transaction_id</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>トランザクションID</t>
         </is>
@@ -3572,34 +3564,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>items</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>フィールド名</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -3633,27 +3625,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>items.item_name</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
@@ -3687,27 +3679,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>items.item_variant</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>バリアント</t>
         </is>
@@ -3741,27 +3733,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>items.item_category2</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>サブカテゴリ2</t>
         </is>
@@ -3795,27 +3787,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>items.item_category4</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>サブカテゴリ4</t>
         </is>
@@ -3849,27 +3841,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>items.price_in_usd</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>単価（USD）</t>
         </is>
@@ -3903,27 +3895,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>items.quantity</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>数量（未指定時は1）</t>
         </is>
@@ -3957,27 +3949,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>items.item_revenue</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>商品収益（ローカル通貨）※purchaseのみ</t>
         </is>
@@ -4011,27 +4003,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>items.item_refund</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>商品返金額（ローカル通貨）※refundのみ</t>
         </is>
@@ -4065,27 +4057,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>items.affiliation</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>商品アフィリエーション（供給元）</t>
         </is>
@@ -4119,27 +4111,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>items.item_list_id</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>商品リストID</t>
         </is>
@@ -4173,27 +4165,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>items.item_list_index</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>リスト内の位置</t>
         </is>
@@ -4227,27 +4219,27 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>items.promotion_name</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>プロモーション名</t>
         </is>
@@ -4281,27 +4273,27 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>items.creative_slot</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>STRING</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>スカラー</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>スカラー</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>クリエイティブスロット</t>
         </is>
